--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.04379164284793</v>
+        <v>9.269616141962789</v>
       </c>
       <c r="D2" t="n">
-        <v>36.59084320600634</v>
+        <v>5.94601202097603</v>
       </c>
       <c r="E2" t="n">
-        <v>12.21516183875697</v>
+        <v>1.984963798798008</v>
       </c>
       <c r="F2" t="n">
-        <v>3.31577958985613</v>
+        <v>0.538814183351621</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.87622976347881</v>
+        <v>6.642387336565307</v>
       </c>
       <c r="D3" t="n">
-        <v>30.4138126514911</v>
+        <v>4.942244555867304</v>
       </c>
       <c r="E3" t="n">
-        <v>12.21516183875697</v>
+        <v>1.984963798798008</v>
       </c>
       <c r="F3" t="n">
-        <v>3.31577958985613</v>
+        <v>0.538814183351621</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.15626649444572</v>
+        <v>4.41289330534743</v>
       </c>
       <c r="D4" t="n">
-        <v>28.93527259246057</v>
+        <v>4.701981796274843</v>
       </c>
       <c r="E4" t="n">
-        <v>12.21516183875697</v>
+        <v>1.984963798798008</v>
       </c>
       <c r="F4" t="n">
-        <v>3.31577958985613</v>
+        <v>0.538814183351621</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
